--- a/artfynd/A 43752-2026 artfynd.xlsx
+++ b/artfynd/A 43752-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,48 +986,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297914</v>
+        <v>137545389</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626905</v>
+        <v>626761</v>
       </c>
       <c r="R5" t="n">
-        <v>6990967</v>
+        <v>6991066</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1054,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,31 +1080,46 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297914</t>
+          <t>https://artportalen.se/Sighting/137545389</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297912</v>
+        <v>137546751</v>
       </c>
       <c r="B6" t="n">
-        <v>80461</v>
+        <v>79563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626913</v>
+        <v>626805</v>
       </c>
       <c r="R6" t="n">
-        <v>6990959</v>
+        <v>6990865</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1181,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,49 +1211,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297912</t>
+          <t>https://artportalen.se/Sighting/137546751</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297917</v>
+        <v>137545392</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>80158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1263,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626776</v>
+        <v>626797</v>
       </c>
       <c r="R7" t="n">
-        <v>6990891</v>
+        <v>6990885</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1293,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,49 +1323,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297917</t>
+          <t>https://artportalen.se/Sighting/137545392</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129297913</v>
+        <v>129297914</v>
       </c>
       <c r="B8" t="n">
-        <v>80392</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626913</v>
+        <v>626905</v>
       </c>
       <c r="R8" t="n">
-        <v>6990959</v>
+        <v>6990967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1435,2503 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297914</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137545386</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80654</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626749</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991079</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545386</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137545388</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80654</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626774</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991092</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545388</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137546748</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80658</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626759</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991084</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546748</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129297912</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>626913</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6990959</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297912</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137545390</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626774</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6990979</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545390</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137545383</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>626900</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6991188</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545383</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137545384</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>626796</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6991166</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545384</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137545385</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>626800</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6991167</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545385</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137545393</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>626714</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6990860</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545393</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137546746</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>626851</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6991189</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546746</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137546747</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626785</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6991166</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Sannolikt årsfärska.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546747</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137546753</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>626701</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6990847</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546753</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137546754</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626702</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6990837</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546754</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137545387</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>626757</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6991078</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545387</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137546744</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57224</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>627081</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6991088</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546744</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129297917</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>626776</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6990891</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297917</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137545391</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>626742</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6990916</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545391</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137546749</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>626783</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6990914</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546749</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137546750</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>626801</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6990897</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546750</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137546752</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>626725</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6990865</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546752</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129297913</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>626913</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6990959</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129297913</t>
         </is>
@@ -1401,6 +3946,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
